--- a/Backlog&Content/G_19 Siksha Sathi Backlog.xlsx
+++ b/Backlog&Content/G_19 Siksha Sathi Backlog.xlsx
@@ -68,7 +68,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="[$-14009]d/m/yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-14009]d/m/yy;@"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -163,10 +163,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -175,77 +175,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -563,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C7:D12"/>
+  <dimension ref="C7:D13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="7" spans="3:4" x14ac:dyDescent="0.3">
@@ -576,35 +506,35 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="7">
-        <v>0</v>
-      </c>
-    </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>12</v>
+        <v>8</v>
+      </c>
+      <c r="D10" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C13" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D13" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1329,927 +1259,927 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="str">
-        <f>TEXT(C3,"dddd")</f>
+        <f t="shared" ref="B2:BM2" si="0">TEXT(C3,"dddd")</f>
         <v>Saturday</v>
       </c>
       <c r="C2" s="2" t="str">
-        <f>TEXT(D3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="D2" s="2" t="str">
-        <f>TEXT(E3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="E2" s="2" t="str">
-        <f>TEXT(F3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="F2" s="2" t="str">
-        <f>TEXT(G3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="G2" s="2" t="str">
-        <f>TEXT(H3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="H2" s="2" t="str">
-        <f>TEXT(I3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="I2" s="2" t="str">
-        <f>TEXT(J3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="J2" s="2" t="str">
-        <f>TEXT(K3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="K2" s="2" t="str">
-        <f>TEXT(L3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="L2" s="2" t="str">
-        <f>TEXT(M3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="M2" s="2" t="str">
-        <f>TEXT(N3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="N2" s="2" t="str">
-        <f>TEXT(O3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="O2" s="2" t="str">
-        <f>TEXT(P3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="P2" s="2" t="str">
-        <f>TEXT(Q3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="Q2" s="2" t="str">
-        <f>TEXT(R3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="R2" s="2" t="str">
-        <f>TEXT(S3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="S2" s="2" t="str">
-        <f>TEXT(T3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="T2" s="2" t="str">
-        <f>TEXT(U3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="U2" s="2" t="str">
-        <f>TEXT(V3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="V2" s="2" t="str">
-        <f>TEXT(W3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="W2" s="2" t="str">
-        <f>TEXT(X3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="X2" s="2" t="str">
-        <f>TEXT(Y3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="Y2" s="2" t="str">
-        <f>TEXT(Z3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="Z2" s="2" t="str">
-        <f>TEXT(AA3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="AA2" s="2" t="str">
-        <f>TEXT(AB3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="AB2" s="2" t="str">
-        <f>TEXT(AC3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="AC2" s="2" t="str">
-        <f>TEXT(AD3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="AD2" s="2" t="str">
-        <f>TEXT(AE3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="AE2" s="2" t="str">
-        <f>TEXT(AF3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="AF2" s="2" t="str">
-        <f>TEXT(AG3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="AG2" s="2" t="str">
-        <f>TEXT(AH3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="AH2" s="2" t="str">
-        <f>TEXT(AI3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="AI2" s="2" t="str">
-        <f>TEXT(AJ3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="AJ2" s="2" t="str">
-        <f>TEXT(AK3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="AK2" s="2" t="str">
-        <f>TEXT(AL3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="AL2" s="2" t="str">
-        <f>TEXT(AM3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="AM2" s="2" t="str">
-        <f>TEXT(AN3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="AN2" s="2" t="str">
-        <f>TEXT(AO3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="AO2" s="2" t="str">
-        <f>TEXT(AP3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="AP2" s="2" t="str">
-        <f>TEXT(AQ3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="AQ2" s="2" t="str">
-        <f>TEXT(AR3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="AR2" s="2" t="str">
-        <f>TEXT(AS3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="AS2" s="2" t="str">
-        <f>TEXT(AT3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="AT2" s="2" t="str">
-        <f>TEXT(AU3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="AU2" s="2" t="str">
-        <f>TEXT(AV3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="AV2" s="2" t="str">
-        <f>TEXT(AW3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="AW2" s="2" t="str">
-        <f>TEXT(AX3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="AX2" s="2" t="str">
-        <f>TEXT(AY3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="AY2" s="2" t="str">
-        <f>TEXT(AZ3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="AZ2" s="2" t="str">
-        <f>TEXT(BA3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="BA2" s="2" t="str">
-        <f>TEXT(BB3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="BB2" s="2" t="str">
-        <f>TEXT(BC3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="BC2" s="2" t="str">
-        <f>TEXT(BD3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="BD2" s="2" t="str">
-        <f>TEXT(BE3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="BE2" s="2" t="str">
-        <f>TEXT(BF3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="BF2" s="2" t="str">
-        <f>TEXT(BG3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="BG2" s="2" t="str">
-        <f>TEXT(BH3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="BH2" s="2" t="str">
-        <f>TEXT(BI3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="BI2" s="2" t="str">
-        <f>TEXT(BJ3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="BJ2" s="2" t="str">
-        <f>TEXT(BK3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="BK2" s="2" t="str">
-        <f>TEXT(BL3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="BL2" s="2" t="str">
-        <f>TEXT(BM3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="BM2" s="2" t="str">
-        <f>TEXT(BN3,"dddd")</f>
+        <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
       <c r="BN2" s="2" t="str">
-        <f>TEXT(BO3,"dddd")</f>
+        <f t="shared" ref="BN2:DY2" si="1">TEXT(BO3,"dddd")</f>
         <v>Saturday</v>
       </c>
       <c r="BO2" s="2" t="str">
-        <f>TEXT(BP3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="BP2" s="2" t="str">
-        <f>TEXT(BQ3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="BQ2" s="2" t="str">
-        <f>TEXT(BR3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="BR2" s="2" t="str">
-        <f>TEXT(BS3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="BS2" s="2" t="str">
-        <f>TEXT(BT3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="BT2" s="2" t="str">
-        <f>TEXT(BU3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="BU2" s="2" t="str">
-        <f>TEXT(BV3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="BV2" s="2" t="str">
-        <f>TEXT(BW3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="BW2" s="2" t="str">
-        <f>TEXT(BX3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="BX2" s="2" t="str">
-        <f>TEXT(BY3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="BY2" s="2" t="str">
-        <f>TEXT(BZ3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="BZ2" s="2" t="str">
-        <f>TEXT(CA3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="CA2" s="2" t="str">
-        <f>TEXT(CB3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="CB2" s="2" t="str">
-        <f>TEXT(CC3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="CC2" s="2" t="str">
-        <f>TEXT(CD3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="CD2" s="2" t="str">
-        <f>TEXT(CE3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="CE2" s="2" t="str">
-        <f>TEXT(CF3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="CF2" s="2" t="str">
-        <f>TEXT(CG3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="CG2" s="2" t="str">
-        <f>TEXT(CH3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="CH2" s="2" t="str">
-        <f>TEXT(CI3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="CI2" s="2" t="str">
-        <f>TEXT(CJ3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="CJ2" s="2" t="str">
-        <f>TEXT(CK3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="CK2" s="2" t="str">
-        <f>TEXT(CL3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="CL2" s="2" t="str">
-        <f>TEXT(CM3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="CM2" s="2" t="str">
-        <f>TEXT(CN3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="CN2" s="2" t="str">
-        <f>TEXT(CO3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="CO2" s="2" t="str">
-        <f>TEXT(CP3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="CP2" s="2" t="str">
-        <f>TEXT(CQ3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="CQ2" s="2" t="str">
-        <f>TEXT(CR3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="CR2" s="2" t="str">
-        <f>TEXT(CS3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="CS2" s="2" t="str">
-        <f>TEXT(CT3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="CT2" s="2" t="str">
-        <f>TEXT(CU3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="CU2" s="2" t="str">
-        <f>TEXT(CV3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="CV2" s="2" t="str">
-        <f>TEXT(CW3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="CW2" s="2" t="str">
-        <f>TEXT(CX3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="CX2" s="2" t="str">
-        <f>TEXT(CY3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="CY2" s="2" t="str">
-        <f>TEXT(CZ3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="CZ2" s="2" t="str">
-        <f>TEXT(DA3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="DA2" s="2" t="str">
-        <f>TEXT(DB3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="DB2" s="2" t="str">
-        <f>TEXT(DC3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="DC2" s="2" t="str">
-        <f>TEXT(DD3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="DD2" s="2" t="str">
-        <f>TEXT(DE3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="DE2" s="2" t="str">
-        <f>TEXT(DF3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="DF2" s="2" t="str">
-        <f>TEXT(DG3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="DG2" s="2" t="str">
-        <f>TEXT(DH3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="DH2" s="2" t="str">
-        <f>TEXT(DI3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="DI2" s="2" t="str">
-        <f>TEXT(DJ3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="DJ2" s="2" t="str">
-        <f>TEXT(DK3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="DK2" s="2" t="str">
-        <f>TEXT(DL3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="DL2" s="2" t="str">
-        <f>TEXT(DM3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="DM2" s="2" t="str">
-        <f>TEXT(DN3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="DN2" s="2" t="str">
-        <f>TEXT(DO3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="DO2" s="2" t="str">
-        <f>TEXT(DP3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="DP2" s="2" t="str">
-        <f>TEXT(DQ3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="DQ2" s="2" t="str">
-        <f>TEXT(DR3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="DR2" s="2" t="str">
-        <f>TEXT(DS3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="DS2" s="2" t="str">
-        <f>TEXT(DT3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="DT2" s="2" t="str">
-        <f>TEXT(DU3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="DU2" s="2" t="str">
-        <f>TEXT(DV3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="DV2" s="2" t="str">
-        <f>TEXT(DW3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="DW2" s="2" t="str">
-        <f>TEXT(DX3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="DX2" s="2" t="str">
-        <f>TEXT(DY3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="DY2" s="2" t="str">
-        <f>TEXT(DZ3,"dddd")</f>
+        <f t="shared" si="1"/>
         <v>Saturday</v>
       </c>
       <c r="DZ2" s="2" t="str">
-        <f>TEXT(EA3,"dddd")</f>
+        <f t="shared" ref="DZ2:GK2" si="2">TEXT(EA3,"dddd")</f>
         <v>Saturday</v>
       </c>
       <c r="EA2" s="2" t="str">
-        <f>TEXT(EB3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="EB2" s="2" t="str">
-        <f>TEXT(EC3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="EC2" s="2" t="str">
-        <f>TEXT(ED3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="ED2" s="2" t="str">
-        <f>TEXT(EE3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="EE2" s="2" t="str">
-        <f>TEXT(EF3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="EF2" s="2" t="str">
-        <f>TEXT(EG3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="EG2" s="2" t="str">
-        <f>TEXT(EH3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="EH2" s="2" t="str">
-        <f>TEXT(EI3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="EI2" s="2" t="str">
-        <f>TEXT(EJ3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="EJ2" s="2" t="str">
-        <f>TEXT(EK3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="EK2" s="2" t="str">
-        <f>TEXT(EL3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="EL2" s="2" t="str">
-        <f>TEXT(EM3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="EM2" s="2" t="str">
-        <f>TEXT(EN3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="EN2" s="2" t="str">
-        <f>TEXT(EO3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="EO2" s="2" t="str">
-        <f>TEXT(EP3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="EP2" s="2" t="str">
-        <f>TEXT(EQ3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="EQ2" s="2" t="str">
-        <f>TEXT(ER3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="ER2" s="2" t="str">
-        <f>TEXT(ES3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="ES2" s="2" t="str">
-        <f>TEXT(ET3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="ET2" s="2" t="str">
-        <f>TEXT(EU3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="EU2" s="2" t="str">
-        <f>TEXT(EV3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="EV2" s="2" t="str">
-        <f>TEXT(EW3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="EW2" s="2" t="str">
-        <f>TEXT(EX3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="EX2" s="2" t="str">
-        <f>TEXT(EY3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="EY2" s="2" t="str">
-        <f>TEXT(EZ3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="EZ2" s="2" t="str">
-        <f>TEXT(FA3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="FA2" s="2" t="str">
-        <f>TEXT(FB3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="FB2" s="2" t="str">
-        <f>TEXT(FC3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="FC2" s="2" t="str">
-        <f>TEXT(FD3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="FD2" s="2" t="str">
-        <f>TEXT(FE3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="FE2" s="2" t="str">
-        <f>TEXT(FF3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="FF2" s="2" t="str">
-        <f>TEXT(FG3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="FG2" s="2" t="str">
-        <f>TEXT(FH3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="FH2" s="2" t="str">
-        <f>TEXT(FI3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="FI2" s="2" t="str">
-        <f>TEXT(FJ3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="FJ2" s="2" t="str">
-        <f>TEXT(FK3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="FK2" s="2" t="str">
-        <f>TEXT(FL3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="FL2" s="2" t="str">
-        <f>TEXT(FM3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="FM2" s="2" t="str">
-        <f>TEXT(FN3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="FN2" s="2" t="str">
-        <f>TEXT(FO3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="FO2" s="2" t="str">
-        <f>TEXT(FP3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="FP2" s="2" t="str">
-        <f>TEXT(FQ3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="FQ2" s="2" t="str">
-        <f>TEXT(FR3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="FR2" s="2" t="str">
-        <f>TEXT(FS3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="FS2" s="2" t="str">
-        <f>TEXT(FT3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="FT2" s="2" t="str">
-        <f>TEXT(FU3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="FU2" s="2" t="str">
-        <f>TEXT(FV3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="FV2" s="2" t="str">
-        <f>TEXT(FW3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="FW2" s="2" t="str">
-        <f>TEXT(FX3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="FX2" s="2" t="str">
-        <f>TEXT(FY3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="FY2" s="2" t="str">
-        <f>TEXT(FZ3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="FZ2" s="2" t="str">
-        <f>TEXT(GA3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="GA2" s="2" t="str">
-        <f>TEXT(GB3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="GB2" s="2" t="str">
-        <f>TEXT(GC3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="GC2" s="2" t="str">
-        <f>TEXT(GD3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="GD2" s="2" t="str">
-        <f>TEXT(GE3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="GE2" s="2" t="str">
-        <f>TEXT(GF3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="GF2" s="2" t="str">
-        <f>TEXT(GG3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="GG2" s="2" t="str">
-        <f>TEXT(GH3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="GH2" s="2" t="str">
-        <f>TEXT(GI3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="GI2" s="2" t="str">
-        <f>TEXT(GJ3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="GJ2" s="2" t="str">
-        <f>TEXT(GK3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="GK2" s="2" t="str">
-        <f>TEXT(GL3,"dddd")</f>
+        <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="GL2" s="2" t="str">
-        <f>TEXT(GM3,"dddd")</f>
+        <f t="shared" ref="GL2:HX2" si="3">TEXT(GM3,"dddd")</f>
         <v>Saturday</v>
       </c>
       <c r="GM2" s="2" t="str">
-        <f>TEXT(GN3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="GN2" s="2" t="str">
-        <f>TEXT(GO3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="GO2" s="2" t="str">
-        <f>TEXT(GP3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="GP2" s="2" t="str">
-        <f>TEXT(GQ3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="GQ2" s="2" t="str">
-        <f>TEXT(GR3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="GR2" s="2" t="str">
-        <f>TEXT(GS3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="GS2" s="2" t="str">
-        <f>TEXT(GT3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="GT2" s="2" t="str">
-        <f>TEXT(GU3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="GU2" s="2" t="str">
-        <f>TEXT(GV3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="GV2" s="2" t="str">
-        <f>TEXT(GW3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="GW2" s="2" t="str">
-        <f>TEXT(GX3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="GX2" s="2" t="str">
-        <f>TEXT(GY3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="GY2" s="2" t="str">
-        <f>TEXT(GZ3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="GZ2" s="2" t="str">
-        <f>TEXT(HA3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="HA2" s="2" t="str">
-        <f>TEXT(HB3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="HB2" s="2" t="str">
-        <f>TEXT(HC3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="HC2" s="2" t="str">
-        <f>TEXT(HD3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="HD2" s="2" t="str">
-        <f>TEXT(HE3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="HE2" s="2" t="str">
-        <f>TEXT(HF3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="HF2" s="2" t="str">
-        <f>TEXT(HG3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="HG2" s="2" t="str">
-        <f>TEXT(HH3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="HH2" s="2" t="str">
-        <f>TEXT(HI3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="HI2" s="2" t="str">
-        <f>TEXT(HJ3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="HJ2" s="2" t="str">
-        <f>TEXT(HK3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="HK2" s="2" t="str">
-        <f>TEXT(HL3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="HL2" s="2" t="str">
-        <f>TEXT(HM3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="HM2" s="2" t="str">
-        <f>TEXT(HN3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="HN2" s="2" t="str">
-        <f>TEXT(HO3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="HO2" s="2" t="str">
-        <f>TEXT(HP3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="HP2" s="2" t="str">
-        <f>TEXT(HQ3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="HQ2" s="2" t="str">
-        <f>TEXT(HR3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="HR2" s="2" t="str">
-        <f>TEXT(HS3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="HS2" s="2" t="str">
-        <f>TEXT(HT3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="HT2" s="2" t="str">
-        <f>TEXT(HU3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="HU2" s="2" t="str">
-        <f>TEXT(HV3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="HV2" s="2" t="str">
-        <f>TEXT(HW3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="HW2" s="2" t="str">
-        <f>TEXT(HX3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="HX2" s="2" t="str">
-        <f>TEXT(HY3,"dddd")</f>
+        <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
     </row>
@@ -3778,7 +3708,7 @@
         <v>Saturday</v>
       </c>
       <c r="GN2" s="2" t="str">
-        <f t="shared" ref="GN2:HC5" si="3">TEXT(GN3,"dddd")</f>
+        <f t="shared" ref="GN2:HC2" si="3">TEXT(GN3,"dddd")</f>
         <v>Saturday</v>
       </c>
       <c r="GO2" s="2" t="str">
@@ -3842,7 +3772,7 @@
         <v>Saturday</v>
       </c>
       <c r="HD2" s="2" t="str">
-        <f t="shared" ref="HD2:HS5" si="4">TEXT(HD3,"dddd")</f>
+        <f t="shared" ref="HD2:HS2" si="4">TEXT(HD3,"dddd")</f>
         <v>Saturday</v>
       </c>
       <c r="HE2" s="2" t="str">
